--- a/CrCraft队伍注册表.xlsx
+++ b/CrCraft队伍注册表.xlsx
@@ -56,28 +56,28 @@
     <t>加入时间</t>
   </si>
   <si>
+    <t>xiaomin</t>
+  </si>
+  <si>
     <t>加粗表示队长</t>
   </si>
   <si>
-    <t>xiaomin</t>
+    <t>XXX</t>
   </si>
   <si>
     <t>下划线表示副队长或管理员</t>
   </si>
   <si>
-    <t>XXX</t>
+    <t>cgh</t>
   </si>
   <si>
     <t>删除线表示玩家被此队伍拉黑</t>
   </si>
   <si>
-    <t>cgh</t>
+    <t>blue_fish233</t>
   </si>
   <si>
     <t>默认加入条件：管理员批准</t>
-  </si>
-  <si>
-    <t>blue_fish233</t>
   </si>
   <si>
     <t>Verbalize_</t>
@@ -1439,7 +1439,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
@@ -1482,9 +1482,6 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="3"/>
@@ -1494,14 +1491,14 @@
       <c r="E2" s="6"/>
       <c r="F2" s="4"/>
       <c r="G2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H2" s="4">
         <v>920634333</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1512,14 +1509,14 @@
       <c r="E3" s="6"/>
       <c r="F3" s="4"/>
       <c r="G3" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H3" s="4">
         <v>920634333</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1530,14 +1527,14 @@
       <c r="E4" s="6"/>
       <c r="F4" s="4"/>
       <c r="G4" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4" s="4">
         <v>2336143095</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1548,13 +1545,15 @@
       <c r="E5" s="6"/>
       <c r="F5" s="4"/>
       <c r="G5" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4">
         <v>2382134650</v>
       </c>
       <c r="I5" s="8"/>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="3"/>
@@ -1666,7 +1665,7 @@
         <v>3012312191</v>
       </c>
       <c r="I12" s="8"/>
-      <c r="J12" s="11"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
@@ -1692,7 +1691,7 @@
         <v>3264155797</v>
       </c>
       <c r="I13" s="8"/>
-      <c r="J13" s="1"/>
+      <c r="J13" s="11"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="3"/>
@@ -2285,6 +2284,9 @@
         <v>45893</v>
       </c>
       <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="J47" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/CrCraft队伍注册表.xlsx
+++ b/CrCraft队伍注册表.xlsx
@@ -80,7 +80,7 @@
     <t>默认加入条件：管理员批准</t>
   </si>
   <si>
-    <t>Verbalize_</t>
+    <t>Verebalize_</t>
   </si>
   <si>
     <t>HUMIANTY</t>

--- a/CrCraft队伍注册表.xlsx
+++ b/CrCraft队伍注册表.xlsx
@@ -143,7 +143,7 @@
     <t>Xuan_Air</t>
   </si>
   <si>
-    <t>moqi</t>
+    <t>Press_on</t>
   </si>
   <si>
     <t>Arknights</t>

--- a/CrCraft队伍注册表.xlsx
+++ b/CrCraft队伍注册表.xlsx
@@ -1937,7 +1937,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="18"/>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>47</v>
       </c>
       <c r="C28" s="20"/>
@@ -2028,7 +2028,7 @@
       <c r="D33" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="27">
         <v>7</v>
       </c>
       <c r="F33" s="27"/>

--- a/CrCraft队伍注册表.xlsx
+++ b/CrCraft队伍注册表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>注册时间</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Press_on</t>
+  </si>
+  <si>
+    <t>aKoishi</t>
   </si>
   <si>
     <t>Arknights</t>
@@ -1439,7 +1442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
@@ -1858,41 +1861,41 @@
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="14">
-        <v>3</v>
-      </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="H24" s="14">
-        <v>3486811922</v>
-      </c>
-      <c r="I24" s="16"/>
+      <c r="H24" s="4">
+        <v>2133498209</v>
+      </c>
+      <c r="I24" s="12"/>
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
+      <c r="B25" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="14">
+        <v>3</v>
+      </c>
       <c r="F25" s="14"/>
-      <c r="G25" s="17" t="s">
+      <c r="G25" s="15" t="s">
         <v>42</v>
       </c>
       <c r="H25" s="14">
-        <v>985304787</v>
+        <v>3486811922</v>
       </c>
       <c r="I25" s="16"/>
       <c r="J25" s="1"/>
@@ -1904,85 +1907,85 @@
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H26" s="14">
-        <v>3486811922</v>
+        <v>985304787</v>
       </c>
       <c r="I26" s="16"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20" t="s">
+      <c r="A27" s="13"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="20">
-        <v>4</v>
-      </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27" s="20">
-        <v>1765654884</v>
-      </c>
-      <c r="I27" s="22"/>
+      <c r="H27" s="14">
+        <v>3486811922</v>
+      </c>
+      <c r="I27" s="16"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="18"/>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="19"/>
+      <c r="C28" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="20">
+        <v>4</v>
+      </c>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="23" t="s">
-        <v>48</v>
-      </c>
       <c r="H28" s="20">
-        <v>2667055602</v>
+        <v>1765654884</v>
       </c>
       <c r="I28" s="22"/>
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
+      <c r="B29" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="C29" s="20"/>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
       <c r="F29" s="20"/>
-      <c r="G29" s="24" t="s">
+      <c r="G29" s="23" t="s">
         <v>49</v>
       </c>
       <c r="H29" s="20">
-        <v>1409004244</v>
+        <v>2667055602</v>
       </c>
       <c r="I29" s="22"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="25"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="28" t="s">
+      <c r="A30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="H30" s="27">
-        <v>758737003</v>
-      </c>
-      <c r="I30" s="27"/>
+      <c r="H30" s="20">
+        <v>1409004244</v>
+      </c>
+      <c r="I30" s="22"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10">
@@ -1992,11 +1995,11 @@
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
       <c r="F31" s="27"/>
-      <c r="G31" s="29" t="s">
+      <c r="G31" s="28" t="s">
         <v>51</v>
       </c>
       <c r="H31" s="27">
-        <v>1983383774</v>
+        <v>758737003</v>
       </c>
       <c r="I31" s="27"/>
       <c r="J31" s="1"/>
@@ -2008,51 +2011,51 @@
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
       <c r="F32" s="27"/>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="29" t="s">
         <v>52</v>
       </c>
       <c r="H32" s="27">
-        <v>2705525405</v>
+        <v>1983383774</v>
       </c>
       <c r="I32" s="27"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="25"/>
-      <c r="B33" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E33" s="27">
-        <v>7</v>
-      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
       <c r="F33" s="27"/>
       <c r="G33" s="28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H33" s="27">
-        <v>2408450176</v>
+        <v>2705525405</v>
       </c>
       <c r="I33" s="27"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
+      <c r="B34" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="27">
+        <v>7</v>
+      </c>
       <c r="F34" s="27"/>
       <c r="G34" s="28" t="s">
         <v>56</v>
       </c>
       <c r="H34" s="27">
-        <v>2307916860</v>
+        <v>2408450176</v>
       </c>
       <c r="I34" s="27"/>
       <c r="J34" s="1"/>
@@ -2068,7 +2071,7 @@
         <v>57</v>
       </c>
       <c r="H35" s="27">
-        <v>2949047592</v>
+        <v>2307916860</v>
       </c>
       <c r="I35" s="27"/>
       <c r="J35" s="1"/>
@@ -2084,49 +2087,49 @@
         <v>58</v>
       </c>
       <c r="H36" s="27">
+        <v>2949047592</v>
+      </c>
+      <c r="I36" s="27"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="25"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="H37" s="27">
         <v>354672662</v>
       </c>
-      <c r="I36" s="30">
+      <c r="I37" s="30">
         <v>46038</v>
       </c>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="31"/>
-      <c r="B37" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="32">
-        <v>3</v>
-      </c>
-      <c r="F37" s="32"/>
-      <c r="G37" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="H37" s="32">
-        <v>3782933040</v>
-      </c>
-      <c r="I37" s="34"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="31"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
+      <c r="B38" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="32">
+        <v>3</v>
+      </c>
       <c r="F38" s="32"/>
-      <c r="G38" s="35" t="s">
+      <c r="G38" s="33" t="s">
         <v>63</v>
       </c>
       <c r="H38" s="32">
-        <v>3950242464</v>
+        <v>3782933040</v>
       </c>
       <c r="I38" s="34"/>
       <c r="J38" s="1"/>
@@ -2142,41 +2145,41 @@
         <v>64</v>
       </c>
       <c r="H39" s="32">
-        <v>362273762</v>
+        <v>3950242464</v>
       </c>
       <c r="I39" s="34"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="36"/>
-      <c r="B40" s="37" t="s">
+      <c r="A40" s="31"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="E40" s="37">
-        <v>3</v>
-      </c>
-      <c r="F40" s="37"/>
-      <c r="G40" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="H40" s="37">
-        <v>2573888108</v>
-      </c>
-      <c r="I40" s="39"/>
+      <c r="H40" s="32">
+        <v>362273762</v>
+      </c>
+      <c r="I40" s="34"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="36"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
+      <c r="B41" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="37">
+        <v>3</v>
+      </c>
       <c r="F41" s="37"/>
       <c r="G41" s="38" t="s">
         <v>68</v>
@@ -2194,55 +2197,53 @@
       <c r="D42" s="37"/>
       <c r="E42" s="37"/>
       <c r="F42" s="37"/>
-      <c r="G42" s="40" t="s">
+      <c r="G42" s="38" t="s">
         <v>69</v>
       </c>
       <c r="H42" s="37">
-        <v>3626117581</v>
+        <v>2573888108</v>
       </c>
       <c r="I42" s="39"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="41">
+      <c r="A43" s="36"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="H43" s="37">
+        <v>3626117581</v>
+      </c>
+      <c r="I43" s="39"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="41">
         <v>45891</v>
       </c>
-      <c r="B43" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="42" t="s">
+      <c r="B44" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="42" t="s">
+      <c r="C44" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="42">
+      <c r="D44" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="42">
         <v>4</v>
       </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="43" t="s">
-        <v>73</v>
-      </c>
-      <c r="H43" s="42">
+      <c r="F44" s="42"/>
+      <c r="G44" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H44" s="42">
         <v>1299972820</v>
-      </c>
-      <c r="I43" s="44">
-        <v>45892</v>
-      </c>
-      <c r="J43" s="1"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="41"/>
-      <c r="B44" s="42"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="H44" s="46">
-        <v>3973229304</v>
       </c>
       <c r="I44" s="44">
         <v>45892</v>
@@ -2256,14 +2257,14 @@
       <c r="D45" s="42"/>
       <c r="E45" s="42"/>
       <c r="F45" s="42"/>
-      <c r="G45" s="47" t="s">
+      <c r="G45" s="45" t="s">
         <v>75</v>
       </c>
       <c r="H45" s="46">
-        <v>1691294516</v>
+        <v>3973229304</v>
       </c>
       <c r="I45" s="44">
-        <v>45893</v>
+        <v>45892</v>
       </c>
       <c r="J45" s="1"/>
     </row>
@@ -2274,11 +2275,11 @@
       <c r="D46" s="42"/>
       <c r="E46" s="42"/>
       <c r="F46" s="42"/>
-      <c r="G46" s="48" t="s">
+      <c r="G46" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="H46" s="42">
-        <v>3040913141</v>
+      <c r="H46" s="46">
+        <v>1691294516</v>
       </c>
       <c r="I46" s="44">
         <v>45893</v>
@@ -2286,30 +2287,48 @@
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10">
+      <c r="A47" s="41"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="H47" s="42">
+        <v>3040913141</v>
+      </c>
+      <c r="I47" s="44">
+        <v>45893</v>
+      </c>
       <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="J48" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E43:E46"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C44:C47"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="D44:D47"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="E44:E47"/>
   </mergeCells>
   <pageMargins left="0.74990626395218" right="0.74990626395218" top="0.999874956025852" bottom="0.999874956025852" header="0.499937478012926" footer="0.499937478012926"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/CrCraft队伍注册表.xlsx
+++ b/CrCraft队伍注册表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="25600" windowHeight="12200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="79">
   <si>
     <t>注册时间</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>aKoishi</t>
+  </si>
+  <si>
+    <t>jet</t>
   </si>
   <si>
     <t>Arknights</t>
@@ -1442,19 +1445,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:J49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="5.125" customWidth="1"/>
-    <col min="5" max="6" width="8.875" customWidth="1"/>
-    <col min="7" max="7" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="23.7545454545455" customWidth="1"/>
+    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="5.12727272727273" customWidth="1"/>
+    <col min="5" max="6" width="8.87272727272727" customWidth="1"/>
+    <col min="7" max="7" width="18.2545454545455" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
     <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="10" width="25.375" customWidth="1"/>
-    <col min="12" max="12" width="30.1083333333333" customWidth="1"/>
+    <col min="10" max="10" width="25.3727272727273" customWidth="1"/>
+    <col min="12" max="12" width="30.1090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1682,7 +1685,7 @@
         <v>26</v>
       </c>
       <c r="E13" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>27</v>
@@ -1877,41 +1880,43 @@
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14" t="s">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="14">
-        <v>3</v>
-      </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="H25" s="14">
-        <v>3486811922</v>
-      </c>
-      <c r="I25" s="16"/>
+      <c r="H25" s="4">
+        <v>2534518105</v>
+      </c>
+      <c r="I25" s="12">
+        <v>46227</v>
+      </c>
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="B26" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="14">
+        <v>3</v>
+      </c>
       <c r="F26" s="14"/>
-      <c r="G26" s="17" t="s">
+      <c r="G26" s="15" t="s">
         <v>43</v>
       </c>
       <c r="H26" s="14">
-        <v>985304787</v>
+        <v>3486811922</v>
       </c>
       <c r="I26" s="16"/>
       <c r="J26" s="1"/>
@@ -1923,85 +1928,85 @@
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="17" t="s">
         <v>44</v>
       </c>
       <c r="H27" s="14">
-        <v>3486811922</v>
+        <v>985304787</v>
       </c>
       <c r="I27" s="16"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="20" t="s">
+      <c r="A28" s="13"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="20">
-        <v>4</v>
-      </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="H28" s="20">
-        <v>1765654884</v>
-      </c>
-      <c r="I28" s="22"/>
+      <c r="H28" s="14">
+        <v>3486811922</v>
+      </c>
+      <c r="I28" s="16"/>
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="18"/>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="19"/>
+      <c r="C29" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="20">
+        <v>4</v>
+      </c>
+      <c r="F29" s="20"/>
+      <c r="G29" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="23" t="s">
-        <v>49</v>
-      </c>
       <c r="H29" s="20">
-        <v>2667055602</v>
+        <v>1765654884</v>
       </c>
       <c r="I29" s="22"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
+      <c r="B30" s="20" t="s">
+        <v>49</v>
+      </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
       <c r="E30" s="20"/>
       <c r="F30" s="20"/>
-      <c r="G30" s="24" t="s">
+      <c r="G30" s="23" t="s">
         <v>50</v>
       </c>
       <c r="H30" s="20">
-        <v>1409004244</v>
+        <v>2667055602</v>
       </c>
       <c r="I30" s="22"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="28" t="s">
+      <c r="A31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H31" s="27">
-        <v>758737003</v>
-      </c>
-      <c r="I31" s="27"/>
+      <c r="H31" s="20">
+        <v>1409004244</v>
+      </c>
+      <c r="I31" s="22"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
@@ -2011,11 +2016,11 @@
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
       <c r="F32" s="27"/>
-      <c r="G32" s="29" t="s">
+      <c r="G32" s="28" t="s">
         <v>52</v>
       </c>
       <c r="H32" s="27">
-        <v>1983383774</v>
+        <v>758737003</v>
       </c>
       <c r="I32" s="27"/>
       <c r="J32" s="1"/>
@@ -2027,51 +2032,51 @@
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
-      <c r="G33" s="28" t="s">
+      <c r="G33" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H33" s="27">
-        <v>2705525405</v>
+        <v>1983383774</v>
       </c>
       <c r="I33" s="27"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="25"/>
-      <c r="B34" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="27">
-        <v>7</v>
-      </c>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
       <c r="F34" s="27"/>
       <c r="G34" s="28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H34" s="27">
-        <v>2408450176</v>
+        <v>2705525405</v>
       </c>
       <c r="I34" s="27"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="25"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
+      <c r="B35" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="27">
+        <v>7</v>
+      </c>
       <c r="F35" s="27"/>
       <c r="G35" s="28" t="s">
         <v>57</v>
       </c>
       <c r="H35" s="27">
-        <v>2307916860</v>
+        <v>2408450176</v>
       </c>
       <c r="I35" s="27"/>
       <c r="J35" s="1"/>
@@ -2087,7 +2092,7 @@
         <v>58</v>
       </c>
       <c r="H36" s="27">
-        <v>2949047592</v>
+        <v>2307916860</v>
       </c>
       <c r="I36" s="27"/>
       <c r="J36" s="1"/>
@@ -2103,49 +2108,49 @@
         <v>59</v>
       </c>
       <c r="H37" s="27">
+        <v>2949047592</v>
+      </c>
+      <c r="I37" s="27"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="25"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38" s="27">
         <v>354672662</v>
       </c>
-      <c r="I37" s="30">
+      <c r="I38" s="30">
         <v>46038</v>
       </c>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="31"/>
-      <c r="B38" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" s="32">
-        <v>3</v>
-      </c>
-      <c r="F38" s="32"/>
-      <c r="G38" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="H38" s="32">
-        <v>3782933040</v>
-      </c>
-      <c r="I38" s="34"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="31"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
+      <c r="B39" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="32">
+        <v>3</v>
+      </c>
       <c r="F39" s="32"/>
-      <c r="G39" s="35" t="s">
+      <c r="G39" s="33" t="s">
         <v>64</v>
       </c>
       <c r="H39" s="32">
-        <v>3950242464</v>
+        <v>3782933040</v>
       </c>
       <c r="I39" s="34"/>
       <c r="J39" s="1"/>
@@ -2161,41 +2166,41 @@
         <v>65</v>
       </c>
       <c r="H40" s="32">
-        <v>362273762</v>
+        <v>3950242464</v>
       </c>
       <c r="I40" s="34"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="36"/>
-      <c r="B41" s="37" t="s">
+      <c r="A41" s="31"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="37">
-        <v>3</v>
-      </c>
-      <c r="F41" s="37"/>
-      <c r="G41" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="H41" s="37">
-        <v>2573888108</v>
-      </c>
-      <c r="I41" s="39"/>
+      <c r="H41" s="32">
+        <v>362273762</v>
+      </c>
+      <c r="I41" s="34"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="36"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
+      <c r="B42" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="37">
+        <v>3</v>
+      </c>
       <c r="F42" s="37"/>
       <c r="G42" s="38" t="s">
         <v>69</v>
@@ -2213,55 +2218,53 @@
       <c r="D43" s="37"/>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
-      <c r="G43" s="40" t="s">
+      <c r="G43" s="38" t="s">
         <v>70</v>
       </c>
       <c r="H43" s="37">
-        <v>3626117581</v>
+        <v>2573888108</v>
       </c>
       <c r="I43" s="39"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="41">
+      <c r="A44" s="36"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="H44" s="37">
+        <v>3626117581</v>
+      </c>
+      <c r="I44" s="39"/>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="41">
         <v>45891</v>
       </c>
-      <c r="B44" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="C44" s="42" t="s">
+      <c r="B45" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="42" t="s">
+      <c r="C45" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="E44" s="42">
+      <c r="D45" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="E45" s="42">
         <v>4</v>
       </c>
-      <c r="F44" s="42"/>
-      <c r="G44" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H44" s="42">
+      <c r="F45" s="42"/>
+      <c r="G45" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="H45" s="42">
         <v>1299972820</v>
-      </c>
-      <c r="I44" s="44">
-        <v>45892</v>
-      </c>
-      <c r="J44" s="1"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="41"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="H45" s="46">
-        <v>3973229304</v>
       </c>
       <c r="I45" s="44">
         <v>45892</v>
@@ -2275,14 +2278,14 @@
       <c r="D46" s="42"/>
       <c r="E46" s="42"/>
       <c r="F46" s="42"/>
-      <c r="G46" s="47" t="s">
+      <c r="G46" s="45" t="s">
         <v>76</v>
       </c>
       <c r="H46" s="46">
-        <v>1691294516</v>
+        <v>3973229304</v>
       </c>
       <c r="I46" s="44">
-        <v>45893</v>
+        <v>45892</v>
       </c>
       <c r="J46" s="1"/>
     </row>
@@ -2293,11 +2296,11 @@
       <c r="D47" s="42"/>
       <c r="E47" s="42"/>
       <c r="F47" s="42"/>
-      <c r="G47" s="48" t="s">
+      <c r="G47" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="H47" s="42">
-        <v>3040913141</v>
+      <c r="H47" s="46">
+        <v>1691294516</v>
       </c>
       <c r="I47" s="44">
         <v>45893</v>
@@ -2305,30 +2308,48 @@
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10">
+      <c r="A48" s="41"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" s="42">
+        <v>3040913141</v>
+      </c>
+      <c r="I48" s="44">
+        <v>45893</v>
+      </c>
       <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="10:10">
+      <c r="J49" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D45:D48"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="E45:E48"/>
   </mergeCells>
   <pageMargins left="0.74990626395218" right="0.74990626395218" top="0.999874956025852" bottom="0.999874956025852" header="0.499937478012926" footer="0.499937478012926"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/CrCraft队伍注册表.xlsx
+++ b/CrCraft队伍注册表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>注册时间</t>
   </si>
@@ -147,9 +147,6 @@
   </si>
   <si>
     <t>aKoishi</t>
-  </si>
-  <si>
-    <t>jet</t>
   </si>
   <si>
     <t>Arknights</t>
@@ -1445,19 +1442,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
-    <col min="2" max="2" width="23.7545454545455" customWidth="1"/>
-    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
-    <col min="4" max="4" width="5.12727272727273" customWidth="1"/>
-    <col min="5" max="6" width="8.87272727272727" customWidth="1"/>
-    <col min="7" max="7" width="18.2545454545455" customWidth="1"/>
+    <col min="2" max="2" width="23.7583333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="5.125" customWidth="1"/>
+    <col min="5" max="6" width="8.875" customWidth="1"/>
+    <col min="7" max="7" width="18.2583333333333" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
     <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="10" width="25.3727272727273" customWidth="1"/>
-    <col min="12" max="12" width="30.1090909090909" customWidth="1"/>
+    <col min="10" max="10" width="25.375" customWidth="1"/>
+    <col min="12" max="12" width="30.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1685,7 +1682,7 @@
         <v>26</v>
       </c>
       <c r="E13" s="6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>27</v>
@@ -1880,43 +1877,41 @@
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="3"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="9" t="s">
+      <c r="A25" s="13"/>
+      <c r="B25" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="4">
-        <v>2534518105</v>
-      </c>
-      <c r="I25" s="12">
-        <v>46227</v>
-      </c>
+      <c r="C25" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="14">
+        <v>3</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="14">
+        <v>3486811922</v>
+      </c>
+      <c r="I25" s="16"/>
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="13"/>
-      <c r="B26" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="14">
-        <v>3</v>
-      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H26" s="14">
-        <v>3486811922</v>
+        <v>985304787</v>
       </c>
       <c r="I26" s="16"/>
       <c r="J26" s="1"/>
@@ -1928,85 +1923,85 @@
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
-      <c r="G27" s="17" t="s">
+      <c r="G27" s="15" t="s">
         <v>44</v>
       </c>
       <c r="H27" s="14">
-        <v>985304787</v>
+        <v>3486811922</v>
       </c>
       <c r="I27" s="16"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15" t="s">
+      <c r="A28" s="18"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H28" s="14">
-        <v>3486811922</v>
-      </c>
-      <c r="I28" s="16"/>
+      <c r="D28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="20">
+        <v>4</v>
+      </c>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" s="20">
+        <v>1765654884</v>
+      </c>
+      <c r="I28" s="22"/>
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="20">
-        <v>4</v>
-      </c>
+      <c r="B29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
       <c r="F29" s="20"/>
-      <c r="G29" s="21" t="s">
-        <v>48</v>
+      <c r="G29" s="23" t="s">
+        <v>49</v>
       </c>
       <c r="H29" s="20">
-        <v>1765654884</v>
+        <v>2667055602</v>
       </c>
       <c r="I29" s="22"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="18"/>
-      <c r="B30" s="20" t="s">
-        <v>49</v>
-      </c>
+      <c r="B30" s="19"/>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
       <c r="E30" s="20"/>
       <c r="F30" s="20"/>
-      <c r="G30" s="23" t="s">
+      <c r="G30" s="24" t="s">
         <v>50</v>
       </c>
       <c r="H30" s="20">
-        <v>2667055602</v>
+        <v>1409004244</v>
       </c>
       <c r="I30" s="22"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="24" t="s">
+      <c r="A31" s="25"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="H31" s="20">
-        <v>1409004244</v>
-      </c>
-      <c r="I31" s="22"/>
+      <c r="H31" s="27">
+        <v>758737003</v>
+      </c>
+      <c r="I31" s="27"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
@@ -2016,11 +2011,11 @@
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
       <c r="F32" s="27"/>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="29" t="s">
         <v>52</v>
       </c>
       <c r="H32" s="27">
-        <v>758737003</v>
+        <v>1983383774</v>
       </c>
       <c r="I32" s="27"/>
       <c r="J32" s="1"/>
@@ -2032,51 +2027,51 @@
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
-      <c r="G33" s="29" t="s">
+      <c r="G33" s="28" t="s">
         <v>53</v>
       </c>
       <c r="H33" s="27">
-        <v>1983383774</v>
+        <v>2705525405</v>
       </c>
       <c r="I33" s="27"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
+      <c r="B34" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="27">
+        <v>7</v>
+      </c>
       <c r="F34" s="27"/>
       <c r="G34" s="28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H34" s="27">
-        <v>2705525405</v>
+        <v>2408450176</v>
       </c>
       <c r="I34" s="27"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="25"/>
-      <c r="B35" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E35" s="27">
-        <v>7</v>
-      </c>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
       <c r="F35" s="27"/>
       <c r="G35" s="28" t="s">
         <v>57</v>
       </c>
       <c r="H35" s="27">
-        <v>2408450176</v>
+        <v>2307916860</v>
       </c>
       <c r="I35" s="27"/>
       <c r="J35" s="1"/>
@@ -2092,7 +2087,7 @@
         <v>58</v>
       </c>
       <c r="H36" s="27">
-        <v>2307916860</v>
+        <v>2949047592</v>
       </c>
       <c r="I36" s="27"/>
       <c r="J36" s="1"/>
@@ -2108,49 +2103,49 @@
         <v>59</v>
       </c>
       <c r="H37" s="27">
-        <v>2949047592</v>
-      </c>
-      <c r="I37" s="27"/>
+        <v>354672662</v>
+      </c>
+      <c r="I37" s="30">
+        <v>46038</v>
+      </c>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="25"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="28" t="s">
+      <c r="A38" s="31"/>
+      <c r="B38" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="H38" s="27">
-        <v>354672662</v>
-      </c>
-      <c r="I38" s="30">
-        <v>46038</v>
-      </c>
+      <c r="C38" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="32">
+        <v>3</v>
+      </c>
+      <c r="F38" s="32"/>
+      <c r="G38" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="H38" s="32">
+        <v>3782933040</v>
+      </c>
+      <c r="I38" s="34"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="31"/>
-      <c r="B39" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E39" s="32">
-        <v>3</v>
-      </c>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
       <c r="F39" s="32"/>
-      <c r="G39" s="33" t="s">
+      <c r="G39" s="35" t="s">
         <v>64</v>
       </c>
       <c r="H39" s="32">
-        <v>3782933040</v>
+        <v>3950242464</v>
       </c>
       <c r="I39" s="34"/>
       <c r="J39" s="1"/>
@@ -2166,41 +2161,41 @@
         <v>65</v>
       </c>
       <c r="H40" s="32">
-        <v>3950242464</v>
+        <v>362273762</v>
       </c>
       <c r="I40" s="34"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="31"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="35" t="s">
+      <c r="A41" s="36"/>
+      <c r="B41" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="H41" s="32">
-        <v>362273762</v>
-      </c>
-      <c r="I41" s="34"/>
+      <c r="C41" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="37">
+        <v>3</v>
+      </c>
+      <c r="F41" s="37"/>
+      <c r="G41" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="37">
+        <v>2573888108</v>
+      </c>
+      <c r="I41" s="39"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="36"/>
-      <c r="B42" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="E42" s="37">
-        <v>3</v>
-      </c>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
       <c r="F42" s="37"/>
       <c r="G42" s="38" t="s">
         <v>69</v>
@@ -2218,53 +2213,55 @@
       <c r="D43" s="37"/>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
-      <c r="G43" s="38" t="s">
+      <c r="G43" s="40" t="s">
         <v>70</v>
       </c>
       <c r="H43" s="37">
-        <v>2573888108</v>
+        <v>3626117581</v>
       </c>
       <c r="I43" s="39"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="36"/>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="40" t="s">
+      <c r="A44" s="41">
+        <v>45891</v>
+      </c>
+      <c r="B44" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="H44" s="37">
-        <v>3626117581</v>
-      </c>
-      <c r="I44" s="39"/>
+      <c r="C44" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="42">
+        <v>4</v>
+      </c>
+      <c r="F44" s="42"/>
+      <c r="G44" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H44" s="42">
+        <v>1299972820</v>
+      </c>
+      <c r="I44" s="44">
+        <v>45892</v>
+      </c>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="41">
-        <v>45891</v>
-      </c>
-      <c r="B45" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="D45" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="E45" s="42">
-        <v>4</v>
-      </c>
+      <c r="A45" s="41"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
       <c r="F45" s="42"/>
-      <c r="G45" s="43" t="s">
+      <c r="G45" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="H45" s="42">
-        <v>1299972820</v>
+      <c r="H45" s="46">
+        <v>3973229304</v>
       </c>
       <c r="I45" s="44">
         <v>45892</v>
@@ -2278,14 +2275,14 @@
       <c r="D46" s="42"/>
       <c r="E46" s="42"/>
       <c r="F46" s="42"/>
-      <c r="G46" s="45" t="s">
+      <c r="G46" s="47" t="s">
         <v>76</v>
       </c>
       <c r="H46" s="46">
-        <v>3973229304</v>
+        <v>1691294516</v>
       </c>
       <c r="I46" s="44">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="J46" s="1"/>
     </row>
@@ -2296,11 +2293,11 @@
       <c r="D47" s="42"/>
       <c r="E47" s="42"/>
       <c r="F47" s="42"/>
-      <c r="G47" s="47" t="s">
+      <c r="G47" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="H47" s="46">
-        <v>1691294516</v>
+      <c r="H47" s="42">
+        <v>3040913141</v>
       </c>
       <c r="I47" s="44">
         <v>45893</v>
@@ -2308,48 +2305,30 @@
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="41"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="42"/>
-      <c r="D48" s="42"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="H48" s="42">
-        <v>3040913141</v>
-      </c>
-      <c r="I48" s="44">
-        <v>45893</v>
-      </c>
       <c r="J48" s="1"/>
-    </row>
-    <row r="49" spans="10:10">
-      <c r="J49" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="E45:E48"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C44:C47"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="D44:D47"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="E44:E47"/>
   </mergeCells>
   <pageMargins left="0.74990626395218" right="0.74990626395218" top="0.999874956025852" bottom="0.999874956025852" header="0.499937478012926" footer="0.499937478012926"/>
   <pageSetup paperSize="9" orientation="portrait"/>
